--- a/tools/importer/reports/import-homepage.report.xlsx
+++ b/tools/importer/reports/import-homepage.report.xlsx
@@ -52,7 +52,7 @@
     <t>homepage</t>
   </si>
   <si>
-    <t>2026-08-09T22:26:46.604Z</t>
+    <t>2026-08-10T04:50:45.428Z</t>
   </si>
   <si>
     <t>Hyundai Motor Brasil</t>
